--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/150.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/150.xlsx
@@ -426,13 +426,13 @@
         <v>3.198929127450154</v>
       </c>
       <c r="E2">
-        <v>-15.41114632302109</v>
+        <v>-16.41939294693287</v>
       </c>
       <c r="F2">
-        <v>0.4185664460804572</v>
+        <v>-0.1288642938966101</v>
       </c>
       <c r="G2">
-        <v>-6.70856677399487</v>
+        <v>-8.043709789982941</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>2.323118038153625</v>
       </c>
       <c r="E3">
-        <v>-15.23789596443564</v>
+        <v>-16.93893118441087</v>
       </c>
       <c r="F3">
-        <v>0.1923152857212311</v>
+        <v>-0.6021246733618152</v>
       </c>
       <c r="G3">
-        <v>-6.680625769643422</v>
+        <v>-7.993978774892009</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>1.273002043522983</v>
       </c>
       <c r="E4">
-        <v>-15.12263724399241</v>
+        <v>-16.88636012965582</v>
       </c>
       <c r="F4">
-        <v>0.09276126288538368</v>
+        <v>-0.1660969235502394</v>
       </c>
       <c r="G4">
-        <v>-7.444699680107211</v>
+        <v>-7.758208342676193</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.173259364118588</v>
       </c>
       <c r="E5">
-        <v>-16.77078441603206</v>
+        <v>-18.09692538680828</v>
       </c>
       <c r="F5">
-        <v>0.06644237376363779</v>
+        <v>0.1838120943314941</v>
       </c>
       <c r="G5">
-        <v>-7.430139900825497</v>
+        <v>-7.91429725430729</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.9451557434383718</v>
       </c>
       <c r="E6">
-        <v>-16.61476037257178</v>
+        <v>-18.75703198595838</v>
       </c>
       <c r="F6">
-        <v>-0.3845440346076914</v>
+        <v>0.103023078271264</v>
       </c>
       <c r="G6">
-        <v>-6.705911716472375</v>
+        <v>-8.580978225551261</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.016455762480599</v>
       </c>
       <c r="E7">
-        <v>-16.71811826332285</v>
+        <v>-18.66490923922034</v>
       </c>
       <c r="F7">
-        <v>0.3854184960900322</v>
+        <v>0.224856042405404</v>
       </c>
       <c r="G7">
-        <v>-6.61390834539049</v>
+        <v>-7.650469948646152</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.995809024834941</v>
       </c>
       <c r="E8">
-        <v>-18.79583195125609</v>
+        <v>-19.4344554697138</v>
       </c>
       <c r="F8">
-        <v>0.6692155115543372</v>
+        <v>-0.02087500579805529</v>
       </c>
       <c r="G8">
-        <v>-5.756788241999944</v>
+        <v>-6.785808422517146</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.830558314365249</v>
       </c>
       <c r="E9">
-        <v>-19.01054048938177</v>
+        <v>-20.75548379333537</v>
       </c>
       <c r="F9">
-        <v>0.3615374922347253</v>
+        <v>0.2154109972786841</v>
       </c>
       <c r="G9">
-        <v>-4.871945630263541</v>
+        <v>-6.526814513343343</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.484827162912608</v>
       </c>
       <c r="E10">
-        <v>-19.08695848826121</v>
+        <v>-20.92905114510135</v>
       </c>
       <c r="F10">
-        <v>0.5934430884854609</v>
+        <v>0.1285293389708635</v>
       </c>
       <c r="G10">
-        <v>-5.962922670548203</v>
+        <v>-6.770334932666592</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.923861088090867</v>
       </c>
       <c r="E11">
-        <v>-19.73332569727203</v>
+        <v>-21.79355947553567</v>
       </c>
       <c r="F11">
-        <v>0.6438061698408653</v>
+        <v>0.3966122248040619</v>
       </c>
       <c r="G11">
-        <v>-6.144171728277762</v>
+        <v>-6.612511295172917</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.130201127747675</v>
       </c>
       <c r="E12">
-        <v>-21.23921991530872</v>
+        <v>-23.1155161363288</v>
       </c>
       <c r="F12">
-        <v>0.8701310548989405</v>
+        <v>0.2827854316179791</v>
       </c>
       <c r="G12">
-        <v>-5.449533199954645</v>
+        <v>-6.336295928103826</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.097732632966278</v>
       </c>
       <c r="E13">
-        <v>-21.99909785379581</v>
+        <v>-23.23506332165729</v>
       </c>
       <c r="F13">
-        <v>0.8441037511029801</v>
+        <v>0.5657250868203866</v>
       </c>
       <c r="G13">
-        <v>-3.131512387175735</v>
+        <v>-5.507434641436499</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.826954254461094</v>
       </c>
       <c r="E14">
-        <v>-22.21300485202212</v>
+        <v>-23.48016244884844</v>
       </c>
       <c r="F14">
-        <v>0.6151338889277659</v>
+        <v>0.9096872551174225</v>
       </c>
       <c r="G14">
-        <v>-3.960472990209241</v>
+        <v>-5.055819950605741</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.333301902709782</v>
       </c>
       <c r="E15">
-        <v>-23.95825156373423</v>
+        <v>-24.73944050090142</v>
       </c>
       <c r="F15">
-        <v>1.06203230416628</v>
+        <v>0.7768502584044938</v>
       </c>
       <c r="G15">
-        <v>-1.92239852932218</v>
+        <v>-3.834632533170464</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.64489024972003</v>
       </c>
       <c r="E16">
-        <v>-24.72678341604998</v>
+        <v>-25.46580320325774</v>
       </c>
       <c r="F16">
-        <v>2.014656474120517</v>
+        <v>1.13158037457052</v>
       </c>
       <c r="G16">
-        <v>-4.276656573573953</v>
+        <v>-4.525242127572287</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.79153621467374</v>
       </c>
       <c r="E17">
-        <v>-24.80017186581829</v>
+        <v>-25.18036442960626</v>
       </c>
       <c r="F17">
-        <v>1.207750413992741</v>
+        <v>1.263854081449546</v>
       </c>
       <c r="G17">
-        <v>-2.043101019684008</v>
+        <v>-3.724778700540828</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.810478955718477</v>
       </c>
       <c r="E18">
-        <v>-25.72111403933618</v>
+        <v>-27.10452209241341</v>
       </c>
       <c r="F18">
-        <v>1.81208585270512</v>
+        <v>0.9278848302221221</v>
       </c>
       <c r="G18">
-        <v>-2.053651728317665</v>
+        <v>-3.900459420673332</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.7460693025285767</v>
       </c>
       <c r="E19">
-        <v>-27.68189347144336</v>
+        <v>-27.59450298004334</v>
       </c>
       <c r="F19">
-        <v>1.729802461850239</v>
+        <v>1.297098122058695</v>
       </c>
       <c r="G19">
-        <v>-2.066595961376215</v>
+        <v>-2.946485996985869</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.362787818784611</v>
       </c>
       <c r="E20">
-        <v>-26.73185132395217</v>
+        <v>-28.44611874497781</v>
       </c>
       <c r="F20">
-        <v>2.040922347728483</v>
+        <v>1.748608058628594</v>
       </c>
       <c r="G20">
-        <v>-0.9801709212080506</v>
+        <v>-2.031302235382045</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.475248170176651</v>
       </c>
       <c r="E21">
-        <v>-27.80090176836494</v>
+        <v>-29.20964210504107</v>
       </c>
       <c r="F21">
-        <v>2.518549051773845</v>
+        <v>1.914742111464451</v>
       </c>
       <c r="G21">
-        <v>-1.89559966318178</v>
+        <v>-2.496082965822484</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.550696023123251</v>
       </c>
       <c r="E22">
-        <v>-27.80021796878978</v>
+        <v>-29.49681075576348</v>
       </c>
       <c r="F22">
-        <v>2.042367020478966</v>
+        <v>1.943855912203243</v>
       </c>
       <c r="G22">
-        <v>-0.3110368357194798</v>
+        <v>-2.508262462861463</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.554548011533031</v>
       </c>
       <c r="E23">
-        <v>-28.55184049916088</v>
+        <v>-30.60801223623964</v>
       </c>
       <c r="F23">
-        <v>2.489874285758537</v>
+        <v>1.851902160288081</v>
       </c>
       <c r="G23">
-        <v>-0.9266725052934283</v>
+        <v>-2.190734798007806</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.454428469205153</v>
       </c>
       <c r="E24">
-        <v>-30.640698761627</v>
+        <v>-29.81289597726187</v>
       </c>
       <c r="F24">
-        <v>3.043086201839742</v>
+        <v>2.008669034533082</v>
       </c>
       <c r="G24">
-        <v>-0.5965515252083841</v>
+        <v>-2.168977892723716</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.223523180237322</v>
       </c>
       <c r="E25">
-        <v>-31.3080667688484</v>
+        <v>-31.03369332143466</v>
       </c>
       <c r="F25">
-        <v>2.573166628110027</v>
+        <v>2.416591935102476</v>
       </c>
       <c r="G25">
-        <v>-0.3210942730677856</v>
+        <v>-2.211488607993497</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.841405241627629</v>
       </c>
       <c r="E26">
-        <v>-30.68641597097144</v>
+        <v>-31.23694708455793</v>
       </c>
       <c r="F26">
-        <v>2.392199828559642</v>
+        <v>2.400203514405491</v>
       </c>
       <c r="G26">
-        <v>0.2297805046669399</v>
+        <v>-1.932316923757837</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.290915992014564</v>
       </c>
       <c r="E27">
-        <v>-30.04523839317341</v>
+        <v>-32.07422796502112</v>
       </c>
       <c r="F27">
-        <v>3.077680481315455</v>
+        <v>2.442279608263289</v>
       </c>
       <c r="G27">
-        <v>-0.1470522729772208</v>
+        <v>-2.179617986086934</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.563640592835735</v>
       </c>
       <c r="E28">
-        <v>-31.11251820424917</v>
+        <v>-31.34476552220656</v>
       </c>
       <c r="F28">
-        <v>2.86120322794186</v>
+        <v>2.068866493694522</v>
       </c>
       <c r="G28">
-        <v>-0.495056820065408</v>
+        <v>-1.937150320245173</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.657032625331147</v>
       </c>
       <c r="E29">
-        <v>-29.38890627710871</v>
+        <v>-30.91982031403778</v>
       </c>
       <c r="F29">
-        <v>2.502675875601401</v>
+        <v>2.332259163293069</v>
       </c>
       <c r="G29">
-        <v>-0.2169180260379999</v>
+        <v>-2.00779736205322</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.575921192271866</v>
       </c>
       <c r="E30">
-        <v>-30.48928017623253</v>
+        <v>-30.64709296692584</v>
       </c>
       <c r="F30">
-        <v>2.704588773298974</v>
+        <v>2.085568037269765</v>
       </c>
       <c r="G30">
-        <v>-0.7807734528322078</v>
+        <v>-1.574989880431062</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.330961153066835</v>
       </c>
       <c r="E31">
-        <v>-29.29822358510511</v>
+        <v>-30.72371701137262</v>
       </c>
       <c r="F31">
-        <v>2.539751943815901</v>
+        <v>2.354437872135624</v>
       </c>
       <c r="G31">
-        <v>-0.6229961629760823</v>
+        <v>-1.148346634603027</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.937040388891318</v>
       </c>
       <c r="E32">
-        <v>-31.22967209106461</v>
+        <v>-30.32397728953054</v>
       </c>
       <c r="F32">
-        <v>2.588140197283031</v>
+        <v>2.153777465951082</v>
       </c>
       <c r="G32">
-        <v>0.1992307904305454</v>
+        <v>-2.837618706926936</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.411563244098702</v>
       </c>
       <c r="E33">
-        <v>-29.82361261100102</v>
+        <v>-30.78214564725659</v>
       </c>
       <c r="F33">
-        <v>3.207971076632178</v>
+        <v>1.860845214768704</v>
       </c>
       <c r="G33">
-        <v>0.2005550086462539</v>
+        <v>-2.272650936831532</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.774800289649406</v>
       </c>
       <c r="E34">
-        <v>-30.13359797801107</v>
+        <v>-29.97835962479113</v>
       </c>
       <c r="F34">
-        <v>2.278368893536545</v>
+        <v>1.983529740592922</v>
       </c>
       <c r="G34">
-        <v>-1.276921602257241</v>
+        <v>-2.014213199308327</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.048138518888204</v>
       </c>
       <c r="E35">
-        <v>-28.32778971915738</v>
+        <v>-28.97349577096309</v>
       </c>
       <c r="F35">
-        <v>3.57646203209351</v>
+        <v>2.220116441036878</v>
       </c>
       <c r="G35">
-        <v>-2.163800199500296</v>
+        <v>-2.602934133648001</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.253368873006202</v>
       </c>
       <c r="E36">
-        <v>-27.48853215978984</v>
+        <v>-29.57995127430731</v>
       </c>
       <c r="F36">
-        <v>2.634382979176911</v>
+        <v>2.081119704316732</v>
       </c>
       <c r="G36">
-        <v>-0.7791281116991899</v>
+        <v>-2.756043554293754</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.416443980441751</v>
       </c>
       <c r="E37">
-        <v>-28.0186715549198</v>
+        <v>-28.72150430633226</v>
       </c>
       <c r="F37">
-        <v>3.145157633212697</v>
+        <v>2.20377440891445</v>
       </c>
       <c r="G37">
-        <v>-1.383070934428433</v>
+        <v>-2.264308362072569</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.56090117121826</v>
       </c>
       <c r="E38">
-        <v>-27.57601774914403</v>
+        <v>-28.26637908313937</v>
       </c>
       <c r="F38">
-        <v>2.601760214119861</v>
+        <v>2.369765982557026</v>
       </c>
       <c r="G38">
-        <v>-1.049318285886808</v>
+        <v>-3.386176102784171</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.707378042694667</v>
       </c>
       <c r="E39">
-        <v>-27.30963479411683</v>
+        <v>-27.59712949496779</v>
       </c>
       <c r="F39">
-        <v>2.929570046429709</v>
+        <v>2.239694076234641</v>
       </c>
       <c r="G39">
-        <v>-1.522689882001656</v>
+        <v>-3.271723922400488</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.1208883645779495</v>
       </c>
       <c r="E40">
-        <v>-26.81513901790125</v>
+        <v>-27.72827410222992</v>
       </c>
       <c r="F40">
-        <v>3.339492625909461</v>
+        <v>2.35762377316679</v>
       </c>
       <c r="G40">
-        <v>-2.047235891062558</v>
+        <v>-3.084376839787592</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.9076945558609364</v>
       </c>
       <c r="E41">
-        <v>-23.45364370505953</v>
+        <v>-26.22660495044239</v>
       </c>
       <c r="F41">
-        <v>2.850194225158655</v>
+        <v>2.491574095669082</v>
       </c>
       <c r="G41">
-        <v>-2.759201814738219</v>
+        <v>-3.779574850306845</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.638983607816605</v>
       </c>
       <c r="E42">
-        <v>-24.83416712019386</v>
+        <v>-25.62074494143017</v>
       </c>
       <c r="F42">
-        <v>2.780919515997338</v>
+        <v>2.184599360274446</v>
       </c>
       <c r="G42">
-        <v>-2.902018749302378</v>
+        <v>-3.276560629433363</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.305177550832077</v>
       </c>
       <c r="E43">
-        <v>-22.44688242062227</v>
+        <v>-24.98265125443137</v>
       </c>
       <c r="F43">
-        <v>2.601798319020389</v>
+        <v>3.016757372309163</v>
       </c>
       <c r="G43">
-        <v>-1.989046432118788</v>
+        <v>-3.63214963635202</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.901140906842144</v>
       </c>
       <c r="E44">
-        <v>-24.70876914644747</v>
+        <v>-24.29877922368902</v>
       </c>
       <c r="F44">
-        <v>3.613617623578679</v>
+        <v>2.394221045022472</v>
       </c>
       <c r="G44">
-        <v>-1.898992972359533</v>
+        <v>-4.326241924661157</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.423355874890784</v>
       </c>
       <c r="E45">
-        <v>-22.60821383561953</v>
+        <v>-24.67857328176432</v>
       </c>
       <c r="F45">
-        <v>3.301122647811788</v>
+        <v>2.808027010886549</v>
       </c>
       <c r="G45">
-        <v>-2.132674450340068</v>
+        <v>-3.328241555846926</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.87473283285565</v>
       </c>
       <c r="E46">
-        <v>-22.65086753229778</v>
+        <v>-23.4392793855072</v>
       </c>
       <c r="F46">
-        <v>3.599659632841508</v>
+        <v>2.346525306704083</v>
       </c>
       <c r="G46">
-        <v>-2.585355136834471</v>
+        <v>-3.339626521956479</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.26052419687417</v>
       </c>
       <c r="E47">
-        <v>-20.31938268944869</v>
+        <v>-22.92500776330012</v>
       </c>
       <c r="F47">
-        <v>3.01406683498487</v>
+        <v>3.071868655617414</v>
       </c>
       <c r="G47">
-        <v>-2.587530165253772</v>
+        <v>-4.071339849773893</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.586411527356097</v>
       </c>
       <c r="E48">
-        <v>-19.78718736711926</v>
+        <v>-23.33263835110057</v>
       </c>
       <c r="F48">
-        <v>3.728754065628588</v>
+        <v>2.659573631896044</v>
       </c>
       <c r="G48">
-        <v>-3.056919175084877</v>
+        <v>-4.710702199227798</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.860761149667791</v>
       </c>
       <c r="E49">
-        <v>-20.77996019534682</v>
+        <v>-21.07979951634269</v>
       </c>
       <c r="F49">
-        <v>3.031918152515199</v>
+        <v>2.34658660589189</v>
       </c>
       <c r="G49">
-        <v>-2.584977734642994</v>
+        <v>-4.219910512485305</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.094841818910241</v>
       </c>
       <c r="E50">
-        <v>-16.8759582248602</v>
+        <v>-21.12115354098074</v>
       </c>
       <c r="F50">
-        <v>4.014013977926237</v>
+        <v>2.686488945547805</v>
       </c>
       <c r="G50">
-        <v>-1.924199466095544</v>
+        <v>-4.42511798828257</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.298124043362469</v>
       </c>
       <c r="E51">
-        <v>-20.07792445535971</v>
+        <v>-19.86988183097333</v>
       </c>
       <c r="F51">
-        <v>3.314442795648804</v>
+        <v>2.76769048857463</v>
       </c>
       <c r="G51">
-        <v>-3.015163264198049</v>
+        <v>-4.315211186924305</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.47653438059612</v>
       </c>
       <c r="E52">
-        <v>-18.58101925822825</v>
+        <v>-20.39112730315222</v>
       </c>
       <c r="F52">
-        <v>3.844715561611685</v>
+        <v>2.943306034702931</v>
       </c>
       <c r="G52">
-        <v>-2.580948800721701</v>
+        <v>-3.85772689885242</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.641861130007432</v>
       </c>
       <c r="E53">
-        <v>-16.6537958185179</v>
+        <v>-18.70657572856491</v>
       </c>
       <c r="F53">
-        <v>3.557818795326105</v>
+        <v>2.766863777906636</v>
       </c>
       <c r="G53">
-        <v>-3.273915503547485</v>
+        <v>-3.539841695080522</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.799850359562131</v>
       </c>
       <c r="E54">
-        <v>-17.49188956006547</v>
+        <v>-18.75382582636094</v>
       </c>
       <c r="F54">
-        <v>3.297206126731352</v>
+        <v>2.800483897316656</v>
       </c>
       <c r="G54">
-        <v>-3.713589056618092</v>
+        <v>-4.521676670026492</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.946336607553876</v>
       </c>
       <c r="E55">
-        <v>-15.22726763593964</v>
+        <v>-17.53553952102541</v>
       </c>
       <c r="F55">
-        <v>3.640034260053955</v>
+        <v>3.026000295789599</v>
       </c>
       <c r="G55">
-        <v>-2.838754224046906</v>
+        <v>-4.786139600431171</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.084836803116269</v>
       </c>
       <c r="E56">
-        <v>-15.82121775831168</v>
+        <v>-17.75932764953646</v>
       </c>
       <c r="F56">
-        <v>3.687430129372532</v>
+        <v>2.752375632031673</v>
       </c>
       <c r="G56">
-        <v>-3.566203569209738</v>
+        <v>-5.375449811876835</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.212827170288773</v>
       </c>
       <c r="E57">
-        <v>-16.40461200777183</v>
+        <v>-16.96461668898237</v>
       </c>
       <c r="F57">
-        <v>3.305965283648554</v>
+        <v>2.839876080789384</v>
       </c>
       <c r="G57">
-        <v>-4.126837835194236</v>
+        <v>-5.056240389889228</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.319100752790254</v>
       </c>
       <c r="E58">
-        <v>-14.76635049449093</v>
+        <v>-17.31994340199423</v>
       </c>
       <c r="F58">
-        <v>3.222709389462787</v>
+        <v>2.493636730502053</v>
       </c>
       <c r="G58">
-        <v>-3.291779207277393</v>
+        <v>-5.208697633063745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.39861665632622</v>
       </c>
       <c r="E59">
-        <v>-15.07877444475412</v>
+        <v>-15.9020555478226</v>
       </c>
       <c r="F59">
-        <v>3.402027737881602</v>
+        <v>2.744703293146944</v>
       </c>
       <c r="G59">
-        <v>-5.241339612080959</v>
+        <v>-5.52277902001102</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.447478226237202</v>
       </c>
       <c r="E60">
-        <v>-13.70760232844562</v>
+        <v>-15.51510650081518</v>
       </c>
       <c r="F60">
-        <v>3.570802625997584</v>
+        <v>2.791489484057059</v>
       </c>
       <c r="G60">
-        <v>-4.870479058589644</v>
+        <v>-5.970920948571083</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.45606995229643</v>
       </c>
       <c r="E61">
-        <v>-13.74329123210007</v>
+        <v>-15.46970402041428</v>
       </c>
       <c r="F61">
-        <v>3.135704304411949</v>
+        <v>3.146043986333693</v>
       </c>
       <c r="G61">
-        <v>-4.502223904437734</v>
+        <v>-6.116025470102878</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.416098391124569</v>
       </c>
       <c r="E62">
-        <v>-13.44266395662687</v>
+        <v>-14.27086751094168</v>
       </c>
       <c r="F62">
-        <v>2.829248127011466</v>
+        <v>2.700181858716081</v>
       </c>
       <c r="G62">
-        <v>-4.418834572849033</v>
+        <v>-6.2655495699296</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.327258044551959</v>
       </c>
       <c r="E63">
-        <v>-13.21011323091097</v>
+        <v>-15.20099795822114</v>
       </c>
       <c r="F63">
-        <v>3.446903713560862</v>
+        <v>2.64794666703035</v>
       </c>
       <c r="G63">
-        <v>-3.77991583649739</v>
+        <v>-5.942794553669435</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.183540640201105</v>
       </c>
       <c r="E64">
-        <v>-12.48404940783916</v>
+        <v>-14.09603671492755</v>
       </c>
       <c r="F64">
-        <v>3.883998400587243</v>
+        <v>2.416030302003378</v>
       </c>
       <c r="G64">
-        <v>-4.493828360950142</v>
+        <v>-5.376214547896407</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.977259077004673</v>
       </c>
       <c r="E65">
-        <v>-12.47484302018156</v>
+        <v>-14.4193018319651</v>
       </c>
       <c r="F65">
-        <v>3.786267614404958</v>
+        <v>2.658846325316386</v>
       </c>
       <c r="G65">
-        <v>-4.660775861950049</v>
+        <v>-6.34863102078315</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.71131440796459</v>
       </c>
       <c r="E66">
-        <v>-12.16752266012502</v>
+        <v>-15.62973576337134</v>
       </c>
       <c r="F66">
-        <v>2.967290584483588</v>
+        <v>2.451477799903974</v>
       </c>
       <c r="G66">
-        <v>-4.374705000810548</v>
+        <v>-6.230216117388959</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.38470877011852</v>
       </c>
       <c r="E67">
-        <v>-10.62426853152505</v>
+        <v>-13.92357883929344</v>
       </c>
       <c r="F67">
-        <v>3.098474159860528</v>
+        <v>2.110930990408681</v>
       </c>
       <c r="G67">
-        <v>-4.055995471199371</v>
+        <v>-6.438667927814708</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.995710184928427</v>
       </c>
       <c r="E68">
-        <v>-12.58681859696923</v>
+        <v>-14.31753343559073</v>
       </c>
       <c r="F68">
-        <v>3.27161620092407</v>
+        <v>2.23337031948167</v>
       </c>
       <c r="G68">
-        <v>-4.547773700512566</v>
+        <v>-5.769960902700704</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.549031943623745</v>
       </c>
       <c r="E69">
-        <v>-11.93217786594639</v>
+        <v>-13.86707254062573</v>
       </c>
       <c r="F69">
-        <v>3.073190729992282</v>
+        <v>2.289222163248024</v>
       </c>
       <c r="G69">
-        <v>-4.630196352803802</v>
+        <v>-6.633354489888169</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.048651392252949</v>
       </c>
       <c r="E70">
-        <v>-12.31919031158992</v>
+        <v>-13.35339867698767</v>
       </c>
       <c r="F70">
-        <v>3.282822355149142</v>
+        <v>2.127470173972976</v>
       </c>
       <c r="G70">
-        <v>-4.522484443138074</v>
+        <v>-6.70207479419236</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.498064957320538</v>
       </c>
       <c r="E71">
-        <v>-10.80633130052943</v>
+        <v>-13.77518074606209</v>
       </c>
       <c r="F71">
-        <v>2.75770700463609</v>
+        <v>2.04591905990217</v>
       </c>
       <c r="G71">
-        <v>-5.942076165287412</v>
+        <v>-6.012984740193062</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.903703789525462</v>
       </c>
       <c r="E72">
-        <v>-12.24496409413019</v>
+        <v>-14.56833391155753</v>
       </c>
       <c r="F72">
-        <v>3.033057986061451</v>
+        <v>1.809249522717934</v>
       </c>
       <c r="G72">
-        <v>-4.356506931981174</v>
+        <v>-6.386669189029376</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.275684480560209</v>
       </c>
       <c r="E73">
-        <v>-11.75343446838964</v>
+        <v>-14.45014526843134</v>
       </c>
       <c r="F73">
-        <v>2.324172640706941</v>
+        <v>2.008637556571776</v>
       </c>
       <c r="G73">
-        <v>-3.558499929739854</v>
+        <v>-6.335203448075866</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.623458891401595</v>
       </c>
       <c r="E74">
-        <v>-12.35207156135961</v>
+        <v>-14.33401708097865</v>
       </c>
       <c r="F74">
-        <v>2.170899820166948</v>
+        <v>1.76676918556757</v>
       </c>
       <c r="G74">
-        <v>-4.642789668035189</v>
+        <v>-6.410918935104537</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9567906505303599</v>
       </c>
       <c r="E75">
-        <v>-13.41361832434167</v>
+        <v>-13.98368980327126</v>
       </c>
       <c r="F75">
-        <v>2.329659746383085</v>
+        <v>1.734913488725512</v>
       </c>
       <c r="G75">
-        <v>-4.169961001388782</v>
+        <v>-5.588198710412558</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.2900997204187044</v>
       </c>
       <c r="E76">
-        <v>-12.04868644521574</v>
+        <v>-13.92279088481611</v>
       </c>
       <c r="F76">
-        <v>2.576710383859204</v>
+        <v>1.980005865661413</v>
       </c>
       <c r="G76">
-        <v>-4.222419906004073</v>
+        <v>-5.468989276088942</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3662563827133917</v>
       </c>
       <c r="E77">
-        <v>-14.75067744595039</v>
+        <v>-14.97766267711086</v>
       </c>
       <c r="F77">
-        <v>1.400319327386736</v>
+        <v>1.516610513596147</v>
       </c>
       <c r="G77">
-        <v>-3.27943749350699</v>
+        <v>-6.068393340883844</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.002740326253261</v>
       </c>
       <c r="E78">
-        <v>-14.25553862642572</v>
+        <v>-15.0162407471822</v>
       </c>
       <c r="F78">
-        <v>1.770559794802781</v>
+        <v>1.555538811323308</v>
       </c>
       <c r="G78">
-        <v>-3.717945734547773</v>
+        <v>-5.098353839694298</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.610537681143513</v>
       </c>
       <c r="E79">
-        <v>-14.51441790002221</v>
+        <v>-15.23142024660467</v>
       </c>
       <c r="F79">
-        <v>1.655411755609233</v>
+        <v>1.599321342030873</v>
       </c>
       <c r="G79">
-        <v>-3.053261022263982</v>
+        <v>-5.143668587035841</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.184978393122274</v>
       </c>
       <c r="E80">
-        <v>-15.34129913992679</v>
+        <v>-16.18487233502364</v>
       </c>
       <c r="F80">
-        <v>1.485559989869611</v>
+        <v>1.436591879220521</v>
       </c>
       <c r="G80">
-        <v>-2.946449580984936</v>
+        <v>-4.594485498071683</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.719914811090881</v>
       </c>
       <c r="E81">
-        <v>-15.6997278576339</v>
+        <v>-15.82470921177159</v>
       </c>
       <c r="F81">
-        <v>1.230563652265839</v>
+        <v>1.136116514468251</v>
       </c>
       <c r="G81">
-        <v>-2.720074477009573</v>
+        <v>-4.156473838861791</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.21495894097975</v>
       </c>
       <c r="E82">
-        <v>-18.05397733931954</v>
+        <v>-16.58358635750298</v>
       </c>
       <c r="F82">
-        <v>2.282515700754959</v>
+        <v>1.198989600340733</v>
       </c>
       <c r="G82">
-        <v>-2.643283062680638</v>
+        <v>-4.599262615284852</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.669906574028191</v>
       </c>
       <c r="E83">
-        <v>-16.7785416920072</v>
+        <v>-19.28852086634262</v>
       </c>
       <c r="F83">
-        <v>1.53601916184374</v>
+        <v>1.021291538561794</v>
       </c>
       <c r="G83">
-        <v>-2.057366160412727</v>
+        <v>-3.272270162414467</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.082534991141333</v>
       </c>
       <c r="E84">
-        <v>-18.04458981270164</v>
+        <v>-20.31297942720185</v>
       </c>
       <c r="F84">
-        <v>1.432985167548732</v>
+        <v>0.8297299199296031</v>
       </c>
       <c r="G84">
-        <v>-2.449990240279211</v>
+        <v>-3.84450789051411</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.453092529350406</v>
       </c>
       <c r="E85">
-        <v>-18.95032989897578</v>
+        <v>-20.56224475048006</v>
       </c>
       <c r="F85">
-        <v>1.526335546905014</v>
+        <v>0.6568065678604007</v>
       </c>
       <c r="G85">
-        <v>-2.727655626294504</v>
+        <v>-3.26717192228399</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.780709898293854</v>
       </c>
       <c r="E86">
-        <v>-19.08727095296774</v>
+        <v>-20.41222999202796</v>
       </c>
       <c r="F86">
-        <v>0.8691337005459699</v>
+        <v>0.7741613778150066</v>
       </c>
       <c r="G86">
-        <v>-2.749948839955956</v>
+        <v>-3.74621117236207</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.060984094692241</v>
       </c>
       <c r="E87">
-        <v>-22.80564624540595</v>
+        <v>-22.72636172247965</v>
       </c>
       <c r="F87">
-        <v>0.8498874123093262</v>
+        <v>0.2235132588454661</v>
       </c>
       <c r="G87">
-        <v>-0.6577436489562726</v>
+        <v>-3.181405618998091</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.288232157838336</v>
       </c>
       <c r="E88">
-        <v>-21.0416607082501</v>
+        <v>-23.27909367443387</v>
       </c>
       <c r="F88">
-        <v>0.6710528304537465</v>
+        <v>0.2826686318141843</v>
       </c>
       <c r="G88">
-        <v>-1.479934186361968</v>
+        <v>-3.199560650735454</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.458825056982647</v>
       </c>
       <c r="E89">
-        <v>-23.79584690039715</v>
+        <v>-25.39450238000697</v>
       </c>
       <c r="F89">
-        <v>0.1315429395822481</v>
+        <v>0.01661524611784473</v>
       </c>
       <c r="G89">
-        <v>-0.2643846279800702</v>
+        <v>-3.762224281135524</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.565992737692492</v>
       </c>
       <c r="E90">
-        <v>-24.7404911068712</v>
+        <v>-25.79992760096568</v>
       </c>
       <c r="F90">
-        <v>0.2011539659091018</v>
+        <v>-0.1660712441607526</v>
       </c>
       <c r="G90">
-        <v>-1.86153083903714</v>
+        <v>-2.579730519963249</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.600404202565625</v>
       </c>
       <c r="E91">
-        <v>-26.66239811809653</v>
+        <v>-26.86737496557972</v>
       </c>
       <c r="F91">
-        <v>0.2273121517547046</v>
+        <v>-0.02883478817155574</v>
       </c>
       <c r="G91">
-        <v>-2.56001291073135</v>
+        <v>-3.192985907294462</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.558880813157341</v>
       </c>
       <c r="E92">
-        <v>-28.66152013962666</v>
+        <v>-28.75442178389402</v>
       </c>
       <c r="F92">
-        <v>-0.3931888768233071</v>
+        <v>-0.4914465046737733</v>
       </c>
       <c r="G92">
-        <v>-1.474865741141344</v>
+        <v>-3.469608471464884</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.436812272565509</v>
       </c>
       <c r="E93">
-        <v>-29.58007127886851</v>
+        <v>-30.2062324368571</v>
       </c>
       <c r="F93">
-        <v>-0.7634202321979209</v>
+        <v>-0.7778644746005359</v>
       </c>
       <c r="G93">
-        <v>-1.30949405981813</v>
+        <v>-2.886095025258483</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.228332877836555</v>
       </c>
       <c r="E94">
-        <v>-33.42541139705977</v>
+        <v>-32.45233063805455</v>
       </c>
       <c r="F94">
-        <v>-0.9533002650024293</v>
+        <v>-0.89692903487452</v>
       </c>
       <c r="G94">
-        <v>-1.497701884271237</v>
+        <v>-2.698036175354645</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.936750217713645</v>
       </c>
       <c r="E95">
-        <v>-33.87765651078379</v>
+        <v>-33.69709266667594</v>
       </c>
       <c r="F95">
-        <v>-0.4766990798017336</v>
+        <v>-1.090288210770786</v>
       </c>
       <c r="G95">
-        <v>-1.645706443695434</v>
+        <v>-3.610895933989899</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.563201463669552</v>
       </c>
       <c r="E96">
-        <v>-36.12082931777228</v>
+        <v>-36.91931476141176</v>
       </c>
       <c r="F96">
-        <v>-1.526915698581989</v>
+        <v>-1.349318697626192</v>
       </c>
       <c r="G96">
-        <v>-1.197538030771057</v>
+        <v>-3.621469816442332</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.118685825392387</v>
       </c>
       <c r="E97">
-        <v>-38.13111402773131</v>
+        <v>-38.08265256313823</v>
       </c>
       <c r="F97">
-        <v>-1.829057738548692</v>
+        <v>-1.564488787238169</v>
       </c>
       <c r="G97">
-        <v>-1.766216922415983</v>
+        <v>-3.875931588772872</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.603409581316541</v>
       </c>
       <c r="E98">
-        <v>-39.97628151842267</v>
+        <v>-39.89696529617833</v>
       </c>
       <c r="F98">
-        <v>-1.791312349472729</v>
+        <v>-1.686039278087954</v>
       </c>
       <c r="G98">
-        <v>-1.35918865890813</v>
+        <v>-3.695808116526666</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.051900257531623</v>
       </c>
       <c r="E99">
-        <v>-43.66263370691564</v>
+        <v>-40.78458469371078</v>
       </c>
       <c r="F99">
-        <v>-2.226143936754663</v>
+        <v>-1.854807539264714</v>
       </c>
       <c r="G99">
-        <v>-1.746469518274231</v>
+        <v>-4.937709617401163</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.455140880158115</v>
       </c>
       <c r="E100">
-        <v>-44.22066170922183</v>
+        <v>-44.86163776992652</v>
       </c>
       <c r="F100">
-        <v>-2.190995479486477</v>
+        <v>-1.944496534700622</v>
       </c>
       <c r="G100">
-        <v>-2.92803632669551</v>
+        <v>-4.901810061573306</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.872340240304409</v>
       </c>
       <c r="E101">
-        <v>-47.16987795569423</v>
+        <v>-47.31003875470564</v>
       </c>
       <c r="F101">
-        <v>-1.872104679002571</v>
+        <v>-1.749309980313781</v>
       </c>
       <c r="G101">
-        <v>-3.287819794812424</v>
+        <v>-5.176512509330951</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.259509361152418</v>
       </c>
       <c r="E102">
-        <v>-48.4443275277914</v>
+        <v>-48.02418136995225</v>
       </c>
       <c r="F102">
-        <v>-2.631658773284119</v>
+        <v>-2.667406140184529</v>
       </c>
       <c r="G102">
-        <v>-2.510894346565184</v>
+        <v>-5.037764235234556</v>
       </c>
     </row>
   </sheetData>
